--- a/reports/一级子公司A_利润表_2026-12.xlsx
+++ b/reports/一级子公司A_利润表_2026-12.xlsx
@@ -2049,7 +2049,7 @@
         </is>
       </c>
       <c r="F3" s="13" t="n">
-        <v>171381518</v>
+        <v>175133474</v>
       </c>
       <c r="G3" s="13" t="n"/>
       <c r="I3" s="5" t="n"/>
@@ -2081,10 +2081,10 @@
         </is>
       </c>
       <c r="F4" s="14" t="n">
-        <v>166995680</v>
+        <v>166977353</v>
       </c>
       <c r="G4" s="14" t="n">
-        <v>2054288162</v>
+        <v>2053706746</v>
       </c>
       <c r="I4" s="5" t="n"/>
     </row>
@@ -2115,10 +2115,10 @@
         </is>
       </c>
       <c r="F5" s="14" t="n">
-        <v>680271</v>
+        <v>679604</v>
       </c>
       <c r="G5" s="14" t="n">
-        <v>8475722</v>
+        <v>8482393</v>
       </c>
     </row>
     <row r="6" ht="18" customHeight="1">
@@ -2148,10 +2148,10 @@
         </is>
       </c>
       <c r="F6" s="14" t="n">
-        <v>590548</v>
+        <v>588379</v>
       </c>
       <c r="G6" s="14" t="n">
-        <v>7352611</v>
+        <v>7359216</v>
       </c>
     </row>
     <row r="7" ht="18" customHeight="1">
@@ -2181,10 +2181,10 @@
         </is>
       </c>
       <c r="F7" s="14" t="n">
-        <v>498617</v>
+        <v>497704</v>
       </c>
       <c r="G7" s="14" t="n">
-        <v>6231026</v>
+        <v>6235321</v>
       </c>
     </row>
     <row r="8" ht="18" customHeight="1">
@@ -2214,10 +2214,10 @@
         </is>
       </c>
       <c r="F8" s="14" t="n">
-        <v>459058</v>
+        <v>457327</v>
       </c>
       <c r="G8" s="14" t="n">
-        <v>5733542</v>
+        <v>5734707</v>
       </c>
     </row>
     <row r="9" ht="18" customHeight="1">
@@ -2247,10 +2247,10 @@
         </is>
       </c>
       <c r="F9" s="14" t="n">
-        <v>250340</v>
+        <v>248454</v>
       </c>
       <c r="G9" s="14" t="n">
-        <v>3115880</v>
+        <v>3115504</v>
       </c>
     </row>
     <row r="10" ht="18" customHeight="1">
@@ -2280,10 +2280,10 @@
         </is>
       </c>
       <c r="F10" s="14" t="n">
-        <v>199903</v>
+        <v>198876</v>
       </c>
       <c r="G10" s="14" t="n">
-        <v>2492315</v>
+        <v>2491513</v>
       </c>
     </row>
     <row r="11" ht="18" customHeight="1">
@@ -2313,7 +2313,7 @@
         </is>
       </c>
       <c r="F11" s="13" t="n">
-        <v>168702781</v>
+        <v>172463130</v>
       </c>
       <c r="G11" s="13" t="n"/>
     </row>
@@ -2344,7 +2344,7 @@
         </is>
       </c>
       <c r="F12" s="13" t="n">
-        <v>164316943</v>
+        <v>164307009</v>
       </c>
       <c r="G12" s="13" t="n"/>
     </row>
@@ -2375,10 +2375,10 @@
         </is>
       </c>
       <c r="F13" s="14" t="n">
-        <v>84449444</v>
+        <v>84336061</v>
       </c>
       <c r="G13" s="14" t="n">
-        <v>1011094547</v>
+        <v>1010256145</v>
       </c>
     </row>
     <row r="14" ht="20.25" customHeight="1">
@@ -2408,10 +2408,10 @@
         </is>
       </c>
       <c r="F14" s="14" t="n">
-        <v>1547596</v>
+        <v>1551975</v>
       </c>
       <c r="G14" s="14" t="n">
-        <v>19316516</v>
+        <v>19301523</v>
       </c>
     </row>
     <row r="15" ht="18" customHeight="1">
@@ -2441,10 +2441,10 @@
         </is>
       </c>
       <c r="F15" s="14" t="n">
-        <v>1395922</v>
+        <v>1405121</v>
       </c>
       <c r="G15" s="14" t="n">
-        <v>17449513</v>
+        <v>17440930</v>
       </c>
     </row>
     <row r="16" ht="18" customHeight="1">
@@ -2474,10 +2474,10 @@
         </is>
       </c>
       <c r="F16" s="14" t="n">
-        <v>75253685</v>
+        <v>75332348</v>
       </c>
       <c r="G16" s="14" t="n">
-        <v>952209422</v>
+        <v>952418650</v>
       </c>
     </row>
     <row r="17" ht="18" customHeight="1">
@@ -2507,10 +2507,10 @@
         </is>
       </c>
       <c r="F17" s="14" t="n">
-        <v>1602398</v>
+        <v>1605444</v>
       </c>
       <c r="G17" s="14" t="n">
-        <v>19937162</v>
+        <v>19952654</v>
       </c>
     </row>
     <row r="18" ht="18" customHeight="1">
@@ -2540,10 +2540,10 @@
         </is>
       </c>
       <c r="F18" s="14" t="n">
-        <v>697156</v>
+        <v>701678</v>
       </c>
       <c r="G18" s="14" t="n">
-        <v>8723505</v>
+        <v>8730353</v>
       </c>
     </row>
     <row r="19" ht="18" customHeight="1">
@@ -2573,10 +2573,10 @@
         </is>
       </c>
       <c r="F19" s="14" t="n">
-        <v>2495072</v>
+        <v>2497938</v>
       </c>
       <c r="G19" s="14" t="n">
-        <v>31164562</v>
+        <v>31186579</v>
       </c>
     </row>
     <row r="20" ht="18" customHeight="1">
@@ -2606,10 +2606,10 @@
         </is>
       </c>
       <c r="F20" s="14" t="n">
-        <v>1102003</v>
+        <v>1098763</v>
       </c>
       <c r="G20" s="14" t="n">
-        <v>13709451</v>
+        <v>13721435</v>
       </c>
     </row>
     <row r="21" ht="18" customHeight="1">
@@ -2639,10 +2639,10 @@
         </is>
       </c>
       <c r="F21" s="14" t="n">
-        <v>4294921</v>
+        <v>4286740</v>
       </c>
       <c r="G21" s="14" t="n">
-        <v>53584362</v>
+        <v>53633523</v>
       </c>
     </row>
     <row r="22" ht="18" customHeight="1">
@@ -2672,10 +2672,10 @@
         </is>
       </c>
       <c r="F22" s="14" t="n">
-        <v>90917</v>
+        <v>92324</v>
       </c>
       <c r="G22" s="14" t="n">
-        <v>1117588</v>
+        <v>1113063</v>
       </c>
     </row>
     <row r="23" ht="18" customHeight="1">
@@ -2705,10 +2705,10 @@
         </is>
       </c>
       <c r="F23" s="14" t="n">
-        <v>0</v>
+        <v>2266291</v>
       </c>
       <c r="G23" s="14" t="n">
-        <v>0</v>
+        <v>28420615</v>
       </c>
     </row>
     <row r="24" ht="18" customHeight="1">
@@ -2738,10 +2738,10 @@
         </is>
       </c>
       <c r="F24" s="14" t="n">
-        <v>0</v>
+        <v>1510766</v>
       </c>
       <c r="G24" s="14" t="n">
-        <v>0</v>
+        <v>18940023</v>
       </c>
     </row>
     <row r="25" ht="18" customHeight="1">
@@ -2771,7 +2771,7 @@
         </is>
       </c>
       <c r="F25" s="13" t="n">
-        <v>114440805</v>
+        <v>122306044</v>
       </c>
       <c r="G25" s="13" t="n"/>
     </row>
@@ -2802,7 +2802,7 @@
         </is>
       </c>
       <c r="F26" s="13" t="n">
-        <v>102269185</v>
+        <v>101951691</v>
       </c>
       <c r="G26" s="13" t="n"/>
     </row>
@@ -2833,10 +2833,10 @@
         </is>
       </c>
       <c r="F27" s="14" t="n">
-        <v>100169598</v>
+        <v>99850798</v>
       </c>
       <c r="G27" s="14" t="n">
-        <v>1264975637</v>
+        <v>1263822196</v>
       </c>
     </row>
     <row r="28" ht="18" customHeight="1">
@@ -2866,10 +2866,10 @@
         </is>
       </c>
       <c r="F28" s="14" t="n">
-        <v>2099587</v>
+        <v>2100893</v>
       </c>
       <c r="G28" s="14" t="n">
-        <v>26169170</v>
+        <v>26150014</v>
       </c>
     </row>
     <row r="29" ht="18" customHeight="1">
@@ -2899,10 +2899,10 @@
         </is>
       </c>
       <c r="F29" s="14" t="n">
-        <v>0</v>
+        <v>3809852</v>
       </c>
       <c r="G29" s="14" t="n">
-        <v>0</v>
+        <v>47329117</v>
       </c>
     </row>
     <row r="30" ht="18" customHeight="1">
@@ -2932,10 +2932,10 @@
         </is>
       </c>
       <c r="F30" s="14" t="n">
-        <v>0</v>
+        <v>1220742</v>
       </c>
       <c r="G30" s="14" t="n">
-        <v>0</v>
+        <v>15149997</v>
       </c>
     </row>
     <row r="31" ht="18" customHeight="1">
@@ -2965,10 +2965,10 @@
         </is>
       </c>
       <c r="F31" s="14" t="n">
-        <v>0</v>
+        <v>763316</v>
       </c>
       <c r="G31" s="14" t="n">
-        <v>0</v>
+        <v>9472222</v>
       </c>
     </row>
     <row r="32" ht="18" customHeight="1">
@@ -2998,10 +2998,10 @@
         </is>
       </c>
       <c r="F32" s="14" t="n">
-        <v>0</v>
+        <v>915557</v>
       </c>
       <c r="G32" s="14" t="n">
-        <v>0</v>
+        <v>11370767</v>
       </c>
     </row>
     <row r="33" ht="18" customHeight="1">
@@ -3031,10 +3031,10 @@
         </is>
       </c>
       <c r="F33" s="14" t="n">
-        <v>0</v>
+        <v>685773</v>
       </c>
       <c r="G33" s="14" t="n">
-        <v>0</v>
+        <v>8530554</v>
       </c>
     </row>
     <row r="34" ht="18" customHeight="1">
@@ -3064,10 +3064,10 @@
         </is>
       </c>
       <c r="F34" s="14" t="n">
-        <v>0</v>
+        <v>456306</v>
       </c>
       <c r="G34" s="14" t="n">
-        <v>0</v>
+        <v>5688001</v>
       </c>
     </row>
     <row r="35" ht="18" customHeight="1">
@@ -3097,10 +3097,10 @@
         </is>
       </c>
       <c r="F35" s="14" t="n">
-        <v>0</v>
+        <v>379419</v>
       </c>
       <c r="G35" s="14" t="n">
-        <v>0</v>
+        <v>4740091</v>
       </c>
     </row>
     <row r="36" ht="18" customHeight="1">
@@ -3130,10 +3130,10 @@
         </is>
       </c>
       <c r="F36" s="14" t="n">
-        <v>1743948</v>
+        <v>1743568</v>
       </c>
       <c r="G36" s="14" t="n">
-        <v>21808698</v>
+        <v>21826264</v>
       </c>
     </row>
     <row r="37" ht="18" customHeight="1">
@@ -3163,10 +3163,10 @@
         </is>
       </c>
       <c r="F37" s="14" t="n">
-        <v>1347525</v>
+        <v>1342911</v>
       </c>
       <c r="G37" s="14" t="n">
-        <v>16827271</v>
+        <v>16832935</v>
       </c>
     </row>
     <row r="38" ht="18" customHeight="1">
@@ -3196,10 +3196,10 @@
         </is>
       </c>
       <c r="F38" s="14" t="n">
-        <v>1101969</v>
+        <v>1093336</v>
       </c>
       <c r="G38" s="14" t="n">
-        <v>13709639</v>
+        <v>13711279</v>
       </c>
     </row>
     <row r="39" ht="18" customHeight="1">
@@ -3229,10 +3229,10 @@
         </is>
       </c>
       <c r="F39" s="14" t="n">
-        <v>8292340</v>
+        <v>8249894</v>
       </c>
       <c r="G39" s="14" t="n">
-        <v>103429048</v>
+        <v>103419017</v>
       </c>
     </row>
     <row r="40" ht="18" customHeight="1">
@@ -3262,10 +3262,10 @@
         </is>
       </c>
       <c r="F40" s="14" t="n">
-        <v>353408</v>
+        <v>348175</v>
       </c>
       <c r="G40" s="14" t="n">
-        <v>4346672</v>
+        <v>4359691</v>
       </c>
     </row>
     <row r="41" ht="18" customHeight="1">
@@ -3295,10 +3295,10 @@
         </is>
       </c>
       <c r="F41" s="14" t="n">
-        <v>679955</v>
+        <v>688415</v>
       </c>
       <c r="G41" s="14" t="n">
-        <v>8318615</v>
+        <v>8273687</v>
       </c>
     </row>
     <row r="42" ht="18" customHeight="1">
@@ -3328,10 +3328,10 @@
         </is>
       </c>
       <c r="F42" s="14" t="n">
-        <v>772377</v>
+        <v>688415</v>
       </c>
       <c r="G42" s="14" t="n">
-        <v>9434112</v>
+        <v>8273687</v>
       </c>
     </row>
     <row r="43" ht="18" customHeight="1">
@@ -3361,10 +3361,10 @@
         </is>
       </c>
       <c r="F43" s="14" t="n">
-        <v>90999</v>
+        <v>92857</v>
       </c>
       <c r="G43" s="14" t="n">
-        <v>1117407</v>
+        <v>1111370</v>
       </c>
     </row>
     <row r="44" ht="18" customHeight="1">
@@ -3394,10 +3394,10 @@
         </is>
       </c>
       <c r="F44" s="14" t="n">
-        <v>0</v>
+        <v>353567</v>
       </c>
       <c r="G44" s="14" t="n">
-        <v>0</v>
+        <v>4224298</v>
       </c>
     </row>
     <row r="45" ht="18" customHeight="1">
@@ -3427,10 +3427,10 @@
         </is>
       </c>
       <c r="F45" s="14" t="n">
-        <v>0</v>
+        <v>667669</v>
       </c>
       <c r="G45" s="14" t="n">
-        <v>0</v>
+        <v>8285542</v>
       </c>
     </row>
     <row r="46" ht="18" customHeight="1">
@@ -3460,10 +3460,10 @@
         </is>
       </c>
       <c r="F46" s="14" t="n">
-        <v>0</v>
+        <v>236075</v>
       </c>
       <c r="G46" s="14" t="n">
-        <v>0</v>
+        <v>2818394</v>
       </c>
     </row>
     <row r="47" ht="18" customHeight="1">
@@ -3493,10 +3493,10 @@
         </is>
       </c>
       <c r="F47" s="14" t="n">
-        <v>0</v>
+        <v>176953</v>
       </c>
       <c r="G47" s="14" t="n">
-        <v>0</v>
+        <v>2114629</v>
       </c>
     </row>
     <row r="48" ht="18" customHeight="1">
@@ -3526,10 +3526,10 @@
         </is>
       </c>
       <c r="F48" s="14" t="n">
-        <v>0</v>
+        <v>294509</v>
       </c>
       <c r="G48" s="14" t="n">
-        <v>0</v>
+        <v>3525471</v>
       </c>
     </row>
     <row r="49" ht="18" customHeight="1">
@@ -3559,10 +3559,10 @@
         </is>
       </c>
       <c r="F49" s="14" t="n">
-        <v>0</v>
+        <v>950365</v>
       </c>
       <c r="G49" s="14" t="n">
-        <v>0</v>
+        <v>11850137</v>
       </c>
     </row>
     <row r="50" ht="18" customHeight="1">
@@ -3592,10 +3592,10 @@
         </is>
       </c>
       <c r="F50" s="14" t="n">
-        <v>0</v>
+        <v>156416</v>
       </c>
       <c r="G50" s="14" t="n">
-        <v>0</v>
+        <v>1880544</v>
       </c>
     </row>
     <row r="51" ht="18" customHeight="1">
@@ -3625,10 +3625,10 @@
         </is>
       </c>
       <c r="F51" s="14" t="n">
-        <v>0</v>
+        <v>117072</v>
       </c>
       <c r="G51" s="14" t="n">
-        <v>0</v>
+        <v>1410158</v>
       </c>
     </row>
     <row r="52" ht="18" customHeight="1">
@@ -3658,10 +3658,10 @@
         </is>
       </c>
       <c r="F52" s="14" t="n">
-        <v>0</v>
+        <v>194821</v>
       </c>
       <c r="G52" s="14" t="n">
-        <v>0</v>
+        <v>2349512</v>
       </c>
     </row>
     <row r="53" ht="18" customHeight="1">
@@ -3691,10 +3691,10 @@
         </is>
       </c>
       <c r="F53" s="14" t="n">
-        <v>0</v>
+        <v>136274</v>
       </c>
       <c r="G53" s="14" t="n">
-        <v>0</v>
+        <v>1643999</v>
       </c>
     </row>
     <row r="54" ht="18" customHeight="1">
@@ -3724,10 +3724,10 @@
         </is>
       </c>
       <c r="F54" s="14" t="n">
-        <v>0</v>
+        <v>97357</v>
       </c>
       <c r="G54" s="14" t="n">
-        <v>0</v>
+        <v>1173795</v>
       </c>
     </row>
     <row r="55" ht="18" customHeight="1">
@@ -3757,10 +3757,10 @@
         </is>
       </c>
       <c r="F55" s="14" t="n">
-        <v>0</v>
+        <v>77969</v>
       </c>
       <c r="G55" s="14" t="n">
-        <v>0</v>
+        <v>938703</v>
       </c>
     </row>
     <row r="56" ht="18" customHeight="1">
@@ -3790,10 +3790,10 @@
         </is>
       </c>
       <c r="F56" s="14" t="n">
-        <v>0</v>
+        <v>58581</v>
       </c>
       <c r="G56" s="14" t="n">
-        <v>0</v>
+        <v>703866</v>
       </c>
     </row>
     <row r="57" ht="18" customHeight="1">
@@ -3823,7 +3823,7 @@
         </is>
       </c>
       <c r="F57" s="13" t="n">
-        <v>54261976</v>
+        <v>52518590</v>
       </c>
       <c r="G57" s="13" t="n"/>
     </row>
@@ -3854,7 +3854,7 @@
         </is>
       </c>
       <c r="F58" s="13" t="n">
-        <v>62890737</v>
+        <v>58751716</v>
       </c>
       <c r="G58" s="13" t="n"/>
     </row>
@@ -3885,10 +3885,10 @@
         </is>
       </c>
       <c r="F59" s="14" t="n">
-        <v>0</v>
+        <v>381145</v>
       </c>
       <c r="G59" s="14" t="n">
-        <v>0</v>
+        <v>4733260</v>
       </c>
     </row>
     <row r="60" ht="18" customHeight="1">
@@ -3918,10 +3918,10 @@
         </is>
       </c>
       <c r="F60" s="14" t="n">
-        <v>0</v>
+        <v>98340</v>
       </c>
       <c r="G60" s="14" t="n">
-        <v>0</v>
+        <v>1173904</v>
       </c>
     </row>
     <row r="61" ht="18" customHeight="1">
@@ -3951,10 +3951,10 @@
         </is>
       </c>
       <c r="F61" s="14" t="n">
-        <v>151791</v>
+        <v>155310</v>
       </c>
       <c r="G61" s="14" t="n">
-        <v>1861971</v>
+        <v>1854295</v>
       </c>
     </row>
     <row r="62" ht="18" customHeight="1">
@@ -3984,7 +3984,7 @@
         </is>
       </c>
       <c r="F62" s="13" t="n">
-        <v>54110185</v>
+        <v>52744425</v>
       </c>
       <c r="G62" s="13" t="n"/>
     </row>
@@ -4015,10 +4015,10 @@
         </is>
       </c>
       <c r="F63" s="14" t="n">
-        <v>5384744</v>
+        <v>5475595</v>
       </c>
       <c r="G63" s="14" t="n">
-        <v>65803730</v>
+        <v>65563312</v>
       </c>
     </row>
     <row r="64" ht="18" customHeight="1">
@@ -4048,7 +4048,7 @@
         </is>
       </c>
       <c r="F64" s="13" t="n">
-        <v>48725441</v>
+        <v>47268830</v>
       </c>
       <c r="G64" s="13" t="n"/>
     </row>
@@ -4108,7 +4108,7 @@
         </is>
       </c>
       <c r="F66" s="13" t="n">
-        <v>48725441</v>
+        <v>47268830</v>
       </c>
       <c r="G66" s="13" t="n"/>
     </row>
@@ -4201,7 +4201,7 @@
         </is>
       </c>
       <c r="F69" s="13" t="n">
-        <v>48725441</v>
+        <v>47268830</v>
       </c>
       <c r="G69" s="13" t="n"/>
     </row>
@@ -4410,7 +4410,7 @@
         </is>
       </c>
       <c r="F76" s="13" t="n">
-        <v>48725441</v>
+        <v>47268830</v>
       </c>
       <c r="G76" s="13" t="n"/>
     </row>
@@ -4441,7 +4441,7 @@
         </is>
       </c>
       <c r="F77" s="13" t="n">
-        <v>48725441</v>
+        <v>47268830</v>
       </c>
       <c r="G77" s="13" t="n"/>
     </row>
